--- a/data/trans_dic/IP16A09-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,36</t>
+          <t>1,52; 13,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,07</t>
+          <t>1,03; 10,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,99</t>
+          <t>0,0; 9,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,62</t>
+          <t>0,0; 13,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 12,06</t>
+          <t>1,22; 11,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 10,65</t>
+          <t>1,87; 10,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,65</t>
+          <t>1,28; 8,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,04</t>
+          <t>0,0; 4,99</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 12,58</t>
+          <t>1,2; 12,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,39</t>
+          <t>0,0; 7,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,65</t>
+          <t>0,0; 7,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,77</t>
+          <t>0,0; 6,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 6,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,04</t>
+          <t>1,11; 6,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,49</t>
+          <t>0,66; 5,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,12</t>
+          <t>0,0; 9,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,11</t>
+          <t>0,0; 16,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 14,86</t>
+          <t>1,63; 15,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,96</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,15</t>
+          <t>0,81; 8,03</t>
         </is>
       </c>
     </row>
@@ -1007,32 +1008,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,39</t>
+          <t>0,0; 11,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,02</t>
+          <t>0,0; 6,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,18</t>
+          <t>0,0; 9,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 14,25</t>
+          <t>1,84; 14,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1042,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,55</t>
+          <t>0,89; 8,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,02; 7,96</t>
+          <t>1,81; 7,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,15</t>
+          <t>0,61; 4,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,66</t>
+          <t>0,35; 3,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,15</t>
+          <t>0,9; 5,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,6</t>
+          <t>1,38; 5,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,67</t>
+          <t>0,47; 4,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,94</t>
+          <t>1,82; 5,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,08</t>
+          <t>1,35; 4,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,14</t>
+          <t>0,72; 2,88</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1562</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1771</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2267</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2898</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4038</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>440; 3854</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>501; 5267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3100</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4108</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>632; 6096</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1096; 6265</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1289; 8178</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3106</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1124</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2962</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3146</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1124</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>518; 5498</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5169</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3847</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3253</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4818</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1042; 6308</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>930; 8327</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3912</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3863</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>698; 6445</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3973</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>704; 6961</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1435</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3573</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2327</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3910</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>599; 4558</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4446</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>606; 5636</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2815</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5197</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3501</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2277</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8469</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>9083</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2266; 9194</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1138; 8671</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>567; 5130</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1292; 7784</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2640; 10605</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>703; 6388</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4898; 14346</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5103; 15211</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2245; 8960</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A09-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Edad-trans_dic.xlsx
@@ -678,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 13,27</t>
+          <t>1,55; 15,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 10,78</t>
+          <t>1,03; 9,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,91</t>
+          <t>0,0; 11,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,85</t>
+          <t>0,0; 14,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,78</t>
+          <t>1,22; 12,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 10,68</t>
+          <t>1,86; 10,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 8,13</t>
+          <t>1,62; 8,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,99</t>
+          <t>0,0; 5,65</t>
         </is>
       </c>
     </row>
@@ -788,27 +788,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 12,72</t>
+          <t>1,47; 12,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>0,0; 9,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 7,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,38</t>
+          <t>0,0; 6,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,45</t>
+          <t>0,0; 6,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,7</t>
+          <t>1,1; 6,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,95</t>
+          <t>0,58; 5,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 4,02</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,97</t>
+          <t>0,0; 10,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,19</t>
+          <t>0,0; 13,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 15,06</t>
+          <t>1,65; 16,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 9,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,03</t>
+          <t>0,81; 8,08</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,7</t>
+          <t>0,0; 12,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,17 +1018,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,42</t>
+          <t>0,0; 7,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,91</t>
+          <t>0,0; 9,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 14,0</t>
+          <t>1,84; 15,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,35</t>
+          <t>0,0; 6,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,32</t>
+          <t>0,14; 7,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,34</t>
+          <t>1,9; 7,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,64</t>
+          <t>0,66; 4,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,16</t>
+          <t>0,35; 3,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,41</t>
+          <t>0,9; 5,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,54</t>
+          <t>1,3; 5,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,31</t>
+          <t>0,48; 4,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,33</t>
+          <t>1,79; 5,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,02</t>
+          <t>1,29; 3,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,88</t>
+          <t>0,77; 3,18</t>
         </is>
       </c>
     </row>
@@ -1417,27 +1417,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>440; 3854</t>
+          <t>449; 4395</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>501; 5267</t>
+          <t>503; 4789</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3100</t>
+          <t>0; 3566</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4108</t>
+          <t>0; 4199</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>632; 6096</t>
+          <t>630; 6492</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1096; 6265</t>
+          <t>1094; 6051</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1289; 8178</t>
+          <t>1632; 8075</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3106</t>
+          <t>0; 3513</t>
         </is>
       </c>
     </row>
@@ -1580,27 +1580,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>518; 5498</t>
+          <t>636; 5259</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5169</t>
+          <t>0; 6111</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3847</t>
+          <t>0; 4043</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3253</t>
+          <t>0; 3274</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4818</t>
+          <t>0; 5173</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1042; 6308</t>
+          <t>1033; 6478</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>930; 8327</t>
+          <t>806; 7713</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3912</t>
+          <t>0; 3961</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2243</t>
+          <t>0; 2310</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3863</t>
+          <t>0; 3266</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>698; 6445</t>
+          <t>706; 7056</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3973</t>
+          <t>0; 4288</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>704; 6961</t>
+          <t>703; 7006</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3573</t>
+          <t>0; 3918</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1916,17 +1916,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2327</t>
+          <t>0; 2825</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3910</t>
+          <t>0; 3579</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>599; 4558</t>
+          <t>599; 5024</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,17 +1936,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4446</t>
+          <t>0; 4476</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>606; 5636</t>
+          <t>92; 5085</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2815</t>
+          <t>0; 2231</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2266; 9194</t>
+          <t>2376; 9439</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1138; 8671</t>
+          <t>1233; 7573</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>567; 5130</t>
+          <t>570; 5852</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1292; 7784</t>
+          <t>1288; 7196</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2640; 10605</t>
+          <t>2493; 10500</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>703; 6388</t>
+          <t>707; 7017</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4898; 14346</t>
+          <t>4821; 13572</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5103; 15211</t>
+          <t>4866; 14812</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2245; 8960</t>
+          <t>2391; 9879</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A09-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Edad-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,38%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,38%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,62%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 15,14</t>
+          <t>0,0; 13,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,8</t>
+          <t>1,21; 12,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,16</t>
+          <t>1,53; 14,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 12,55</t>
+          <t>1,01; 10,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 10,31</t>
+          <t>1,77; 10,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,03</t>
+          <t>1,59; 8,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,65</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>5,36%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2,65%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,2%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 12,17</t>
+          <t>0,0; 6,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,37</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,43</t>
+          <t>1,37; 12,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,93</t>
+          <t>0,0; 8,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 6,88</t>
+          <t>1,2; 7,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,51</t>
+          <t>0,56; 5,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,27</t>
+          <t>0,0; 12,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>1,64; 14,86</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 10,12</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,69</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,65; 16,49</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,25</t>
+          <t>0,0; 8,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,08</t>
+          <t>0,81; 8,15</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,83</t>
+          <t>0,0; 8,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>1,82; 14,25</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,79</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,07</t>
+          <t>0,0; 14,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 15,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 8,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,4</t>
+          <t>0,0; 6,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 7,51</t>
+          <t>0,88; 7,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,15%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,53</t>
+          <t>0,89; 5,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,05</t>
+          <t>1,36; 5,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,6</t>
+          <t>0,48; 4,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,0</t>
+          <t>2,02; 7,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,48</t>
+          <t>0,68; 4,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,74</t>
+          <t>0,35; 3,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,04</t>
+          <t>1,69; 4,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,91</t>
+          <t>1,35; 4,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,18</t>
+          <t>0,74; 3,14</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2267</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1562</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1771</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>613</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1335</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2267</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>449; 4395</t>
+          <t>0; 4040</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>503; 4789</t>
+          <t>624; 6242</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3566</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4199</t>
+          <t>444; 4169</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>630; 6492</t>
+          <t>492; 4920</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3440</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1094; 6051</t>
+          <t>1042; 6253</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1632; 8075</t>
+          <t>1598; 8703</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 3134</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2315</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1730</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1124</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>636; 5259</t>
+          <t>0; 3452</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6111</t>
+          <t>0; 5040</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4043</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3274</t>
+          <t>594; 5435</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5173</t>
+          <t>0; 5476</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3911</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1033; 6478</t>
+          <t>1127; 6630</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>806; 7713</t>
+          <t>780; 7676</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3961</t>
+          <t>0; 3877</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2310</t>
+          <t>0; 2891</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1753,27 +1753,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>702; 6360</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2279</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3266</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>706; 7056</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4288</t>
+          <t>0; 4157</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>703; 7006</t>
+          <t>704; 7068</t>
         </is>
       </c>
     </row>
@@ -1805,27 +1805,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1899</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>793</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>540</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1899</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3918</t>
+          <t>0; 3225</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>593; 4641</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0; 2825</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3579</t>
+          <t>0; 4396</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>599; 5024</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2906</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4476</t>
+          <t>0; 4443</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>92; 5085</t>
+          <t>598; 5115</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 2231</t>
+          <t>0; 2905</t>
         </is>
       </c>
     </row>
@@ -1963,27 +1963,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>5197</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>3501</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2277</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5582</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2376; 9439</t>
+          <t>1282; 7416</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1233; 7573</t>
+          <t>2611; 10721</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>570; 5852</t>
+          <t>705; 6921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1288; 7196</t>
+          <t>2528; 9976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2493; 10500</t>
+          <t>1267; 7769</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>707; 7017</t>
+          <t>571; 5948</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4821; 13572</t>
+          <t>4546; 13313</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4866; 14812</t>
+          <t>5106; 15444</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2391; 9879</t>
+          <t>2305; 9767</t>
         </is>
       </c>
     </row>
